--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -582,12 +582,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Will Pay</t>
+          <t>Discussed - No Outcome</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Call Back</t>
+          <t>Discussed - No Outcome</t>
         </is>
       </c>
     </row>

--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Discussed - No Outcome</t>
+          <t>Will Pay</t>
         </is>
       </c>
     </row>

--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -622,12 +622,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>19-07-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">

--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -622,12 +622,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Will Pay</t>
+          <t>Wrong Person</t>
         </is>
       </c>
     </row>

--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="1" min="1" max="1"/>
@@ -560,6 +560,11 @@
           <t>Outcome</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -622,12 +627,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,7 +642,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wrong Person</t>
+          <t>Will Pay</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+918750063980</t>
         </is>
       </c>
     </row>

--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -2,24 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="dd\ mmmm\ yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +25,14 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <family val="2"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,14 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF9FBFD"/>
-        <bgColor rgb="FFF9FBFD"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,54 +109,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -252,44 +226,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -319,12 +293,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -363,142 +337,201 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -509,14 +542,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col width="17.85546875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16.140625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="25.7109375" customWidth="1" style="1" min="3" max="3"/>
-    <col width="28.28515625" customWidth="1" style="1" min="4" max="4"/>
-    <col width="37.42578125" customWidth="1" style="1" min="5" max="5"/>
-    <col width="33.85546875" customWidth="1" style="1" min="6" max="6"/>
+    <col width="17.85714285714286" customWidth="1" min="1" max="1"/>
+    <col width="16.14285714285714" customWidth="1" min="2" max="2"/>
+    <col width="25.71428571428572" customWidth="1" min="3" max="3"/>
+    <col width="28.28571428571428" customWidth="1" min="4" max="4"/>
+    <col width="37.42857142857143" customWidth="1" min="5" max="5"/>
+    <col width="33.85714285714285" customWidth="1" min="6" max="6"/>
+    <col width="13.57142857142857" customWidth="1" min="7" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,28 +601,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Rajesh Sharma</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>₹200,000</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>₹18,750</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Mon Jun 15 2026 05:30:00 GMT+0530 (India Standard Time)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -607,32 +641,34 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Amit Verma</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Pradeep Chopra</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>₹100,000</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>₹9,500</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>46193</v>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Sat Jun 20 2026 05:30:00 GMT+0530 (India Standard Time)</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -652,24 +688,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Pooja Malhotra</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>₹150,000</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>₹12,000</t>
         </is>
       </c>
-      <c r="D4" s="16" t="n">
-        <v>46198</v>
-      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Thu Jun 25 2026 05:30:00 GMT+0530 (India Standard Time)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>ICICI Bank</t>
@@ -682,28 +722,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Sanjay Gupta</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>₹250,000</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>₹22,000</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>46201</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Sun Jun 28 2026 05:30:00 GMT+0530 (India Standard Time)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -717,24 +757,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Neha Joshi</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>₹80,000</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>₹8,000</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
-        <v>46205</v>
-      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Thu Jul 02 2026 05:30:00 GMT+0530 (India Standard Time)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Kotak Mahindra Bank</t>
@@ -747,28 +791,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Vikram Singh</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>₹180,000</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>₹15,500</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>46208</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>15500</t>
-        </is>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Sun Jul 05 2026 05:30:00 GMT+0530 (India Standard Time)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -788,6 +832,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Pradeep Chopra</t>
+          <t>Gaurav Mahajan</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -661,14 +661,12 @@
           <t>Sat Jun 20 2026 05:30:00 GMT+0530 (India Standard Time)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
+      <c r="E3" t="n">
+        <v>9500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>05-07-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -678,7 +676,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Will Pay</t>
+          <t>Discussed - No Outcome</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Gaurav Mahajan</t>
+          <t>Pradeep Chopra</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -661,8 +661,10 @@
           <t>Sat Jun 20 2026 05:30:00 GMT+0530 (India Standard Time)</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>9500</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -688,7 +690,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Pooja Malhotra</t>
+          <t>Anubha Sinha</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -722,7 +724,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Sanjay Gupta</t>
+          <t>Ankur Sinha</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">

--- a/data/Customers.xlsx
+++ b/data/Customers.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Discussed - No Outcome</t>
+          <t>Will Pay</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -742,17 +742,14 @@
           <t>Sun Jun 28 2026 05:30:00 GMT+0530 (India Standard Time)</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>19-06-2026</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Axis Bank</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Discussed - No Outcome</t>
         </is>
       </c>
     </row>
@@ -810,9 +807,6 @@
         <is>
           <t>Sun Jul 05 2026 05:30:00 GMT+0530 (India Standard Time)</t>
         </is>
-      </c>
-      <c r="E7" t="n">
-        <v>15500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
